--- a/2022 data/excel_outputs/254_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/254_boothwise_data.xlsx
@@ -14,11 +14,113 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="477">
   <si>
     <t>AC 254 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
+    <t>Unnamed: 27</t>
+  </si>
+  <si>
+    <t>Unnamed: 28</t>
+  </si>
+  <si>
+    <t>Unnamed: 29</t>
+  </si>
+  <si>
+    <t>Unnamed: 30</t>
+  </si>
+  <si>
+    <t>Unnamed: 31</t>
+  </si>
+  <si>
+    <t>Unnamed: 32</t>
+  </si>
+  <si>
+    <t>Unnamed: 33</t>
+  </si>
+  <si>
+    <t>Unnamed: 34</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -43,7 +145,7 @@
     <t>GANDHI SMARK INTER COLLEGE KALYANPUR UTTARI MADHYA BHAG-1</t>
   </si>
   <si>
-    <t>GANDHI SMARK INTER COLLEGE KALYANPUR PASHCHIM BHAG-■</t>
+    <t>GA.CDHI SMARAK INTAR KALEJ KALYANAPUR PASHICHAMI BHAG-1</t>
   </si>
   <si>
     <t>GANDHI SMARK INTER COLLEGE KALYANPUR PASHCHIM BHAG-2</t>
@@ -97,7 +199,7 @@
     <t>SHERVANI HIGHER SECONDARY SCHOOL MUKUNDPUR DAKSHINI BHAG-1</t>
   </si>
   <si>
-    <t>SHERVANI HIGHER SECONDARY SCHOOL MUKUNDPUR DAKSHINI BHAG-■</t>
+    <t>JILA PARISHAD PRAIMARI PATHASHALA HASANAPUR</t>
   </si>
   <si>
     <t>PRATHMIK VIDYALAYA CHAUBARA UTTARI BHAG</t>
@@ -106,7 +208,7 @@
     <t>PRATHMIK VIDYALAYA CHAUBARA DAKSHINI BHAG-2</t>
   </si>
   <si>
-    <t>PRATHMIK VIDYALAYA CHAUBARA DAKSHINI BHAG-■</t>
+    <t>JILA PARISHAD PRAIMARI PATHASHALA BABHANAPUR KALYANAPUR</t>
   </si>
   <si>
     <t>PRATHMIK VIDYALAYA HASANPUR</t>
@@ -844,7 +946,7 @@
     <t>PRATHMIK VIDYALYA PACHDEVRA DAKCHIDI BHAG</t>
   </si>
   <si>
-    <t>PRATHMIK VIDYALYA PACHDEVRA DAKCHIDI BHAG ■</t>
+    <t>JILA PARISHAD PRAIMARI PATHASHALA HATHIAGAHA.C UTTARI BHAG-1</t>
   </si>
   <si>
     <t>PRATHMIK VIDYALYA KANJIYA UTTARI BHAG 1</t>
@@ -874,7 +976,7 @@
     <t>SARSVATI DEVI PARMANAND SINHA INTER COLLAGE KAURIHAR DAKCHIDI BHAG 1</t>
   </si>
   <si>
-    <t>SARSVATI DEVI PARMANAND SINHA INTER COLLAGE KAURIHAR DAKCHIDI BHAG ■</t>
+    <t>JILA PARISHAD PRAIMARI PATHASHALA SHAHAVAPUR (PASIYAPUR)</t>
   </si>
   <si>
     <t>PRATHMIK VIDYALYA KASARI</t>
@@ -1117,7 +1219,7 @@
     <t>PRATHMIK VIDYALYA KORSAND DAKCHIDI BHAG</t>
   </si>
   <si>
-    <t>PRATHMIK VIDYALYA KORSAND DAKCHIDI BHAG ■</t>
+    <t>PRATHMIK VIDYALYA KORSAND DAKCHIDI BHAG ROOM NO. 367</t>
   </si>
   <si>
     <t>PRATHMIK VIDYALYA RANGPURA UTTARI BHAG 1</t>
@@ -1349,8 +1451,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1366,7 +1476,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1374,12 +1484,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1678,115 +1806,217 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:35">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>411</v>
+        <v>445</v>
       </c>
       <c r="D2" t="s">
-        <v>412</v>
+        <v>446</v>
       </c>
       <c r="E2" t="s">
-        <v>413</v>
+        <v>447</v>
       </c>
       <c r="F2" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="G2" t="s">
-        <v>415</v>
+        <v>449</v>
       </c>
       <c r="H2" t="s">
-        <v>416</v>
+        <v>450</v>
       </c>
       <c r="I2" t="s">
-        <v>417</v>
+        <v>451</v>
       </c>
       <c r="J2" t="s">
-        <v>418</v>
+        <v>452</v>
       </c>
       <c r="K2" t="s">
-        <v>419</v>
+        <v>453</v>
       </c>
       <c r="L2" t="s">
-        <v>420</v>
+        <v>454</v>
       </c>
       <c r="M2" t="s">
-        <v>421</v>
+        <v>455</v>
       </c>
       <c r="N2" t="s">
-        <v>422</v>
+        <v>456</v>
       </c>
       <c r="O2" t="s">
-        <v>423</v>
+        <v>457</v>
       </c>
       <c r="P2" t="s">
-        <v>424</v>
+        <v>458</v>
       </c>
       <c r="Q2" t="s">
-        <v>425</v>
+        <v>459</v>
       </c>
       <c r="R2" t="s">
-        <v>426</v>
+        <v>460</v>
       </c>
       <c r="S2" t="s">
-        <v>427</v>
+        <v>461</v>
       </c>
       <c r="T2" t="s">
-        <v>428</v>
+        <v>462</v>
       </c>
       <c r="U2" t="s">
-        <v>429</v>
+        <v>463</v>
       </c>
       <c r="V2" t="s">
-        <v>430</v>
+        <v>464</v>
       </c>
       <c r="W2" t="s">
-        <v>431</v>
+        <v>465</v>
       </c>
       <c r="X2" t="s">
-        <v>432</v>
+        <v>466</v>
       </c>
       <c r="Y2" t="s">
-        <v>433</v>
+        <v>467</v>
       </c>
       <c r="Z2" t="s">
-        <v>434</v>
+        <v>468</v>
       </c>
       <c r="AA2" t="s">
-        <v>435</v>
+        <v>469</v>
       </c>
       <c r="AB2" t="s">
-        <v>436</v>
+        <v>470</v>
       </c>
       <c r="AC2" t="s">
-        <v>437</v>
+        <v>471</v>
       </c>
       <c r="AD2" t="s">
-        <v>438</v>
+        <v>472</v>
       </c>
       <c r="AE2" t="s">
-        <v>439</v>
+        <v>473</v>
       </c>
       <c r="AF2" t="s">
-        <v>440</v>
+        <v>474</v>
       </c>
       <c r="AG2" t="s">
-        <v>440</v>
+        <v>474</v>
       </c>
       <c r="AH2" t="s">
-        <v>441</v>
+        <v>475</v>
       </c>
       <c r="AI2" t="s">
-        <v>442</v>
+        <v>476</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1794,7 +2024,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="C3">
         <v>944</v>
@@ -1901,7 +2131,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="C4">
         <v>1047</v>
@@ -2008,7 +2238,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="C5">
         <v>967</v>
@@ -2115,7 +2345,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C6">
         <v>1080</v>
@@ -2222,7 +2452,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="C7">
         <v>1057</v>
@@ -2329,7 +2559,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="C8">
         <v>1191</v>
@@ -2436,7 +2666,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="C9">
         <v>1099</v>
@@ -2543,7 +2773,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C10">
         <v>666</v>
@@ -2650,7 +2880,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C11">
         <v>1024</v>
@@ -2757,7 +2987,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="C12">
         <v>810</v>
@@ -2864,7 +3094,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="C13">
         <v>765</v>
@@ -2971,7 +3201,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C14">
         <v>779</v>
@@ -3078,7 +3308,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="C15">
         <v>844</v>
@@ -3185,7 +3415,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="C16">
         <v>937</v>
@@ -3292,7 +3522,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="C17">
         <v>638</v>
@@ -3399,7 +3629,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="C18">
         <v>904</v>
@@ -3506,7 +3736,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="C19">
         <v>965</v>
@@ -3613,7 +3843,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C20">
         <v>697</v>
@@ -3720,7 +3950,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="C21">
         <v>810</v>
@@ -3827,7 +4057,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="C22">
         <v>1119</v>
@@ -3934,7 +4164,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="C23">
         <v>620</v>
@@ -4041,7 +4271,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="C24">
         <v>1173</v>
@@ -4148,7 +4378,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="C25">
         <v>927</v>
@@ -4255,7 +4485,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="C26">
         <v>1053</v>
@@ -4362,7 +4592,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="C27">
         <v>912</v>
@@ -4469,7 +4699,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="C28">
         <v>938</v>
@@ -4576,7 +4806,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="C29">
         <v>926</v>
@@ -4683,7 +4913,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="C30">
         <v>947</v>
@@ -4790,7 +5020,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="C31">
         <v>860</v>
@@ -4897,7 +5127,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="C32">
         <v>868</v>
@@ -5004,7 +5234,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="C33">
         <v>791</v>
@@ -5111,7 +5341,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="C34">
         <v>769</v>
@@ -5218,7 +5448,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="C35">
         <v>1007</v>
@@ -5325,7 +5555,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="C36">
         <v>613</v>
@@ -5432,7 +5662,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="C37">
         <v>725</v>
@@ -5539,7 +5769,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="C38">
         <v>674</v>
@@ -5646,7 +5876,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="C39">
         <v>1137</v>
@@ -5753,7 +5983,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="C40">
         <v>682</v>
@@ -5860,7 +6090,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="C41">
         <v>695</v>
@@ -5967,7 +6197,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="C42">
         <v>612</v>
@@ -6074,7 +6304,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="C43">
         <v>1113</v>
@@ -6181,7 +6411,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="C44">
         <v>723</v>
@@ -6288,7 +6518,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="C45">
         <v>903</v>
@@ -6395,7 +6625,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="C46">
         <v>1064</v>
@@ -6502,7 +6732,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="C47">
         <v>826</v>
@@ -6609,7 +6839,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="C48">
         <v>665</v>
@@ -6716,7 +6946,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="C49">
         <v>782</v>
@@ -6823,7 +7053,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C50">
         <v>812</v>
@@ -6930,7 +7160,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="C51">
         <v>443</v>
@@ -7037,7 +7267,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="C52">
         <v>710</v>
@@ -7144,7 +7374,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="C53">
         <v>672</v>
@@ -7251,7 +7481,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="C54">
         <v>1170</v>
@@ -7358,7 +7588,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C55">
         <v>1067</v>
@@ -7465,7 +7695,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="C56">
         <v>803</v>
@@ -7572,7 +7802,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="C57">
         <v>731</v>
@@ -7679,7 +7909,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C58">
         <v>726</v>
@@ -7786,7 +8016,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="C59">
         <v>1168</v>
@@ -7893,7 +8123,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="C60">
         <v>1175</v>
@@ -8000,7 +8230,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="C61">
         <v>591</v>
@@ -8107,7 +8337,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="C62">
         <v>982</v>
@@ -8214,7 +8444,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="C63">
         <v>884</v>
@@ -8321,7 +8551,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="C64">
         <v>1146</v>
@@ -8428,7 +8658,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="C65">
         <v>904</v>
@@ -8535,7 +8765,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="C66">
         <v>1043</v>
@@ -8642,7 +8872,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="C67">
         <v>917</v>
@@ -8749,7 +8979,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="C68">
         <v>1112</v>
@@ -8856,7 +9086,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="C69">
         <v>668</v>
@@ -8963,7 +9193,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="C70">
         <v>1093</v>
@@ -9070,7 +9300,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="C71">
         <v>1192</v>
@@ -9177,7 +9407,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="C72">
         <v>750</v>
@@ -9284,7 +9514,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="C73">
         <v>667</v>
@@ -9391,7 +9621,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="C74">
         <v>877</v>
@@ -9498,7 +9728,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="C75">
         <v>642</v>
@@ -9605,7 +9835,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="C76">
         <v>641</v>
@@ -9712,7 +9942,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="C77">
         <v>1015</v>
@@ -9819,7 +10049,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="C78">
         <v>717</v>
@@ -9926,7 +10156,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="C79">
         <v>722</v>
@@ -10033,7 +10263,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="C80">
         <v>766</v>
@@ -10140,7 +10370,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="C81">
         <v>1017</v>
@@ -10247,7 +10477,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="C82">
         <v>714</v>
@@ -10354,7 +10584,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="C83">
         <v>842</v>
@@ -10461,7 +10691,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="C84">
         <v>781</v>
@@ -10568,7 +10798,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="C85">
         <v>1020</v>
@@ -10675,7 +10905,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="C86">
         <v>844</v>
@@ -10782,7 +11012,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="C87">
         <v>1161</v>
@@ -10889,7 +11119,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="C88">
         <v>703</v>
@@ -10996,7 +11226,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="C89">
         <v>682</v>
@@ -11103,7 +11333,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="C90">
         <v>744</v>
@@ -11210,7 +11440,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="C91">
         <v>853</v>
@@ -11317,7 +11547,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="C92">
         <v>632</v>
@@ -11424,7 +11654,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="C93">
         <v>653</v>
@@ -11531,7 +11761,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="C94">
         <v>936</v>
@@ -11638,7 +11868,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="C95">
         <v>1122</v>
@@ -11745,7 +11975,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="C96">
         <v>1051</v>
@@ -11852,7 +12082,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>131</v>
       </c>
       <c r="C97">
         <v>1024</v>
@@ -11959,7 +12189,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="C98">
         <v>1099</v>
@@ -12066,7 +12296,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="C99">
         <v>1122</v>
@@ -12173,7 +12403,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="C100">
         <v>1129</v>
@@ -12280,7 +12510,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="C101">
         <v>1083</v>
@@ -12387,7 +12617,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="C102">
         <v>1081</v>
@@ -12494,7 +12724,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="C103">
         <v>1096</v>
@@ -12601,7 +12831,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="C104">
         <v>1193</v>
@@ -12708,7 +12938,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="C105">
         <v>727</v>
@@ -12815,7 +13045,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="C106">
         <v>682</v>
@@ -12922,7 +13152,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="C107">
         <v>1019</v>
@@ -13029,7 +13259,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="C108">
         <v>759</v>
@@ -13136,7 +13366,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="C109">
         <v>744</v>
@@ -13243,7 +13473,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="C110">
         <v>692</v>
@@ -13350,7 +13580,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="C111">
         <v>944</v>
@@ -13457,7 +13687,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="C112">
         <v>897</v>
@@ -13564,7 +13794,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="C113">
         <v>781</v>
@@ -13671,7 +13901,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="C114">
         <v>752</v>
@@ -13778,7 +14008,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="C115">
         <v>906</v>
@@ -13885,7 +14115,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="C116">
         <v>924</v>
@@ -13992,7 +14222,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="C117">
         <v>995</v>
@@ -14099,7 +14329,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="C118">
         <v>852</v>
@@ -14206,7 +14436,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="C119">
         <v>909</v>
@@ -14313,7 +14543,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="C120">
         <v>680</v>
@@ -14420,7 +14650,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="C121">
         <v>667</v>
@@ -14527,7 +14757,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="C122">
         <v>1153</v>
@@ -14634,7 +14864,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="C123">
         <v>1165</v>
@@ -14741,7 +14971,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="C124">
         <v>1020</v>
@@ -14848,7 +15078,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="C125">
         <v>1060</v>
@@ -14955,7 +15185,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="C126">
         <v>1088</v>
@@ -15062,7 +15292,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="C127">
         <v>983</v>
@@ -15169,7 +15399,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="C128">
         <v>1050</v>
@@ -15276,7 +15506,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="C129">
         <v>398</v>
@@ -15383,7 +15613,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="C130">
         <v>976</v>
@@ -15490,7 +15720,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="C131">
         <v>1016</v>
@@ -15597,7 +15827,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="C132">
         <v>1162</v>
@@ -15704,7 +15934,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="C133">
         <v>974</v>
@@ -15811,7 +16041,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="C134">
         <v>718</v>
@@ -15918,7 +16148,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="C135">
         <v>667</v>
@@ -16025,7 +16255,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="C136">
         <v>712</v>
@@ -16132,7 +16362,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="C137">
         <v>1206</v>
@@ -16239,7 +16469,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="C138">
         <v>991</v>
@@ -16346,7 +16576,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="C139">
         <v>1055</v>
@@ -16453,7 +16683,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="C140">
         <v>879</v>
@@ -16560,7 +16790,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
       <c r="C141">
         <v>1054</v>
@@ -16667,7 +16897,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="C142">
         <v>852</v>
@@ -16774,7 +17004,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="C143">
         <v>633</v>
@@ -16881,7 +17111,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="C144">
         <v>864</v>
@@ -16988,7 +17218,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="C145">
         <v>936</v>
@@ -17095,7 +17325,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="C146">
         <v>469</v>
@@ -17202,7 +17432,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="C147">
         <v>1143</v>
@@ -17309,7 +17539,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="C148">
         <v>824</v>
@@ -17416,7 +17646,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="C149">
         <v>915</v>
@@ -17523,7 +17753,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="C150">
         <v>916</v>
@@ -17630,7 +17860,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="C151">
         <v>628</v>
@@ -17737,7 +17967,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="C152">
         <v>640</v>
@@ -17844,7 +18074,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="C153">
         <v>1018</v>
@@ -17951,7 +18181,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="C154">
         <v>902</v>
@@ -18058,7 +18288,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="C155">
         <v>658</v>
@@ -18165,7 +18395,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="C156">
         <v>675</v>
@@ -18272,7 +18502,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="C157">
         <v>744</v>
@@ -18379,7 +18609,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="C158">
         <v>1044</v>
@@ -18486,7 +18716,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>157</v>
+        <v>191</v>
       </c>
       <c r="C159">
         <v>667</v>
@@ -18593,7 +18823,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="C160">
         <v>921</v>
@@ -18700,7 +18930,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="C161">
         <v>680</v>
@@ -18807,7 +19037,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="C162">
         <v>1065</v>
@@ -18914,7 +19144,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="C163">
         <v>1206</v>
@@ -19021,7 +19251,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="C164">
         <v>1193</v>
@@ -19128,7 +19358,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="C165">
         <v>1196</v>
@@ -19235,7 +19465,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="C166">
         <v>1058</v>
@@ -19342,7 +19572,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="C167">
         <v>776</v>
@@ -19449,7 +19679,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="C168">
         <v>682</v>
@@ -19556,7 +19786,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="C169">
         <v>920</v>
@@ -19663,7 +19893,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="C170">
         <v>961</v>
@@ -19770,7 +20000,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="C171">
         <v>982</v>
@@ -19877,7 +20107,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="C172">
         <v>1139</v>
@@ -19984,7 +20214,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="C173">
         <v>931</v>
@@ -20091,7 +20321,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="C174">
         <v>950</v>
@@ -20198,7 +20428,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>173</v>
+        <v>207</v>
       </c>
       <c r="C175">
         <v>1028</v>
@@ -20305,7 +20535,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="C176">
         <v>961</v>
@@ -20412,7 +20642,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="C177">
         <v>945</v>
@@ -20519,7 +20749,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>176</v>
+        <v>210</v>
       </c>
       <c r="C178">
         <v>1127</v>
@@ -20626,7 +20856,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>177</v>
+        <v>211</v>
       </c>
       <c r="C179">
         <v>1087</v>
@@ -20733,7 +20963,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="C180">
         <v>1219</v>
@@ -20840,7 +21070,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="C181">
         <v>1006</v>
@@ -20947,7 +21177,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="C182">
         <v>1054</v>
@@ -21054,7 +21284,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="C183">
         <v>959</v>
@@ -21161,7 +21391,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>182</v>
+        <v>216</v>
       </c>
       <c r="C184">
         <v>1025</v>
@@ -21268,7 +21498,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="C185">
         <v>1022</v>
@@ -21375,7 +21605,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="C186">
         <v>588</v>
@@ -21482,7 +21712,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="C187">
         <v>627</v>
@@ -21589,7 +21819,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>186</v>
+        <v>220</v>
       </c>
       <c r="C188">
         <v>825</v>
@@ -21696,7 +21926,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>187</v>
+        <v>221</v>
       </c>
       <c r="C189">
         <v>856</v>
@@ -21803,7 +22033,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="C190">
         <v>432</v>
@@ -21910,7 +22140,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>189</v>
+        <v>223</v>
       </c>
       <c r="C191">
         <v>1031</v>
@@ -22017,7 +22247,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>190</v>
+        <v>224</v>
       </c>
       <c r="C192">
         <v>1116</v>
@@ -22124,7 +22354,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>191</v>
+        <v>225</v>
       </c>
       <c r="C193">
         <v>900</v>
@@ -22231,7 +22461,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="C194">
         <v>512</v>
@@ -22338,7 +22568,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="C195">
         <v>1065</v>
@@ -22445,7 +22675,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="C196">
         <v>1031</v>
@@ -22552,7 +22782,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="C197">
         <v>896</v>
@@ -22659,7 +22889,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="C198">
         <v>621</v>
@@ -22766,7 +22996,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="C199">
         <v>611</v>
@@ -22873,7 +23103,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>198</v>
+        <v>232</v>
       </c>
       <c r="C200">
         <v>912</v>
@@ -22980,7 +23210,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>199</v>
+        <v>233</v>
       </c>
       <c r="C201">
         <v>899</v>
@@ -23087,7 +23317,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>200</v>
+        <v>234</v>
       </c>
       <c r="C202">
         <v>824</v>
@@ -23194,7 +23424,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>201</v>
+        <v>235</v>
       </c>
       <c r="C203">
         <v>833</v>
@@ -23301,7 +23531,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="C204">
         <v>1057</v>
@@ -23408,7 +23638,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>203</v>
+        <v>237</v>
       </c>
       <c r="C205">
         <v>995</v>
@@ -23515,7 +23745,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>204</v>
+        <v>238</v>
       </c>
       <c r="C206">
         <v>884</v>
@@ -23622,7 +23852,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>205</v>
+        <v>239</v>
       </c>
       <c r="C207">
         <v>952</v>
@@ -23729,7 +23959,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="C208">
         <v>631</v>
@@ -23836,7 +24066,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>207</v>
+        <v>241</v>
       </c>
       <c r="C209">
         <v>643</v>
@@ -23943,7 +24173,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="C210">
         <v>948</v>
@@ -24050,7 +24280,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>209</v>
+        <v>243</v>
       </c>
       <c r="C211">
         <v>834</v>
@@ -24157,7 +24387,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>210</v>
+        <v>244</v>
       </c>
       <c r="C212">
         <v>365</v>
@@ -24264,7 +24494,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
       <c r="C213">
         <v>825</v>
@@ -24371,7 +24601,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="C214">
         <v>870</v>
@@ -24478,7 +24708,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>213</v>
+        <v>247</v>
       </c>
       <c r="C215">
         <v>792</v>
@@ -24585,7 +24815,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>214</v>
+        <v>248</v>
       </c>
       <c r="C216">
         <v>752</v>
@@ -24692,7 +24922,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>215</v>
+        <v>249</v>
       </c>
       <c r="C217">
         <v>1097</v>
@@ -24799,7 +25029,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>216</v>
+        <v>250</v>
       </c>
       <c r="C218">
         <v>877</v>
@@ -24906,7 +25136,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>217</v>
+        <v>251</v>
       </c>
       <c r="C219">
         <v>820</v>
@@ -25013,7 +25243,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>218</v>
+        <v>252</v>
       </c>
       <c r="C220">
         <v>568</v>
@@ -25120,7 +25350,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>219</v>
+        <v>253</v>
       </c>
       <c r="C221">
         <v>856</v>
@@ -25227,7 +25457,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>220</v>
+        <v>254</v>
       </c>
       <c r="C222">
         <v>662</v>
@@ -25334,7 +25564,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>221</v>
+        <v>255</v>
       </c>
       <c r="C223">
         <v>770</v>
@@ -25441,7 +25671,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="C224">
         <v>653</v>
@@ -25548,7 +25778,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>223</v>
+        <v>257</v>
       </c>
       <c r="C225">
         <v>896</v>
@@ -25655,7 +25885,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>224</v>
+        <v>258</v>
       </c>
       <c r="C226">
         <v>1046</v>
@@ -25762,7 +25992,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>225</v>
+        <v>259</v>
       </c>
       <c r="C227">
         <v>1092</v>
@@ -25869,7 +26099,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="C228">
         <v>1043</v>
@@ -25976,7 +26206,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>227</v>
+        <v>261</v>
       </c>
       <c r="C229">
         <v>973</v>
@@ -26083,7 +26313,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>228</v>
+        <v>262</v>
       </c>
       <c r="C230">
         <v>753</v>
@@ -26190,7 +26420,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>229</v>
+        <v>263</v>
       </c>
       <c r="C231">
         <v>759</v>
@@ -26297,7 +26527,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>230</v>
+        <v>264</v>
       </c>
       <c r="C232">
         <v>1140</v>
@@ -26404,7 +26634,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="C233">
         <v>799</v>
@@ -26511,7 +26741,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>232</v>
+        <v>266</v>
       </c>
       <c r="C234">
         <v>940</v>
@@ -26618,7 +26848,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>233</v>
+        <v>267</v>
       </c>
       <c r="C235">
         <v>539</v>
@@ -26725,7 +26955,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>234</v>
+        <v>268</v>
       </c>
       <c r="C236">
         <v>952</v>
@@ -26832,7 +27062,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>235</v>
+        <v>269</v>
       </c>
       <c r="C237">
         <v>946</v>
@@ -26939,7 +27169,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>236</v>
+        <v>270</v>
       </c>
       <c r="C238">
         <v>940</v>
@@ -27046,7 +27276,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>237</v>
+        <v>271</v>
       </c>
       <c r="C239">
         <v>775</v>
@@ -27153,7 +27383,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="C240">
         <v>910</v>
@@ -27260,7 +27490,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>239</v>
+        <v>273</v>
       </c>
       <c r="C241">
         <v>1068</v>
@@ -27367,7 +27597,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>240</v>
+        <v>274</v>
       </c>
       <c r="C242">
         <v>939</v>
@@ -27474,7 +27704,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>241</v>
+        <v>275</v>
       </c>
       <c r="C243">
         <v>952</v>
@@ -27581,7 +27811,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>242</v>
+        <v>276</v>
       </c>
       <c r="C244">
         <v>1020</v>
@@ -27688,7 +27918,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="C245">
         <v>894</v>
@@ -27795,7 +28025,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>244</v>
+        <v>278</v>
       </c>
       <c r="C246">
         <v>820</v>
@@ -27902,7 +28132,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>245</v>
+        <v>279</v>
       </c>
       <c r="C247">
         <v>961</v>
@@ -28009,7 +28239,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="C248">
         <v>960</v>
@@ -28116,7 +28346,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>247</v>
+        <v>281</v>
       </c>
       <c r="C249">
         <v>1126</v>
@@ -28223,7 +28453,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>248</v>
+        <v>282</v>
       </c>
       <c r="C250">
         <v>1154</v>
@@ -28330,7 +28560,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="C251">
         <v>920</v>
@@ -28437,7 +28667,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>250</v>
+        <v>284</v>
       </c>
       <c r="C252">
         <v>1101</v>
@@ -28544,7 +28774,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="C253">
         <v>799</v>
@@ -28651,7 +28881,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="C254">
         <v>1089</v>
@@ -28758,7 +28988,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>253</v>
+        <v>287</v>
       </c>
       <c r="C255">
         <v>1094</v>
@@ -28865,7 +29095,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>254</v>
+        <v>288</v>
       </c>
       <c r="C256">
         <v>1180</v>
@@ -28972,7 +29202,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="C257">
         <v>1175</v>
@@ -29079,7 +29309,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="C258">
         <v>605</v>
@@ -29186,7 +29416,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>257</v>
+        <v>291</v>
       </c>
       <c r="C259">
         <v>407</v>
@@ -29293,7 +29523,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>258</v>
+        <v>292</v>
       </c>
       <c r="C260">
         <v>881</v>
@@ -29400,7 +29630,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>259</v>
+        <v>293</v>
       </c>
       <c r="C261">
         <v>1171</v>
@@ -29507,7 +29737,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="C262">
         <v>1022</v>
@@ -29614,7 +29844,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>261</v>
+        <v>295</v>
       </c>
       <c r="C263">
         <v>772</v>
@@ -29721,7 +29951,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>262</v>
+        <v>296</v>
       </c>
       <c r="C264">
         <v>683</v>
@@ -29828,7 +30058,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="C265">
         <v>719</v>
@@ -29935,7 +30165,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>264</v>
+        <v>298</v>
       </c>
       <c r="C266">
         <v>1029</v>
@@ -30042,7 +30272,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="C267">
         <v>798</v>
@@ -30149,7 +30379,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>266</v>
+        <v>300</v>
       </c>
       <c r="C268">
         <v>706</v>
@@ -30256,7 +30486,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="C269">
         <v>718</v>
@@ -30363,7 +30593,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>268</v>
+        <v>302</v>
       </c>
       <c r="C270">
         <v>719</v>
@@ -30470,7 +30700,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>269</v>
+        <v>303</v>
       </c>
       <c r="C271">
         <v>1010</v>
@@ -30577,7 +30807,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="C272">
         <v>927</v>
@@ -30684,7 +30914,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>271</v>
+        <v>305</v>
       </c>
       <c r="C273">
         <v>678</v>
@@ -30791,7 +31021,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>272</v>
+        <v>306</v>
       </c>
       <c r="C274">
         <v>797</v>
@@ -30898,7 +31128,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>273</v>
+        <v>307</v>
       </c>
       <c r="C275">
         <v>698</v>
@@ -31005,7 +31235,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="C276">
         <v>790</v>
@@ -31112,7 +31342,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>275</v>
+        <v>309</v>
       </c>
       <c r="C277">
         <v>867</v>
@@ -31219,7 +31449,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>276</v>
+        <v>310</v>
       </c>
       <c r="C278">
         <v>912</v>
@@ -31326,7 +31556,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="C279">
         <v>865</v>
@@ -31433,7 +31663,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
       <c r="C280">
         <v>950</v>
@@ -31540,7 +31770,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>279</v>
+        <v>313</v>
       </c>
       <c r="C281">
         <v>1125</v>
@@ -31647,7 +31877,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>280</v>
+        <v>314</v>
       </c>
       <c r="C282">
         <v>1092</v>
@@ -31754,7 +31984,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>281</v>
+        <v>315</v>
       </c>
       <c r="C283">
         <v>680</v>
@@ -31861,7 +32091,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="C284">
         <v>722</v>
@@ -31968,7 +32198,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="C285">
         <v>1012</v>
@@ -32075,7 +32305,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>284</v>
+        <v>318</v>
       </c>
       <c r="C286">
         <v>947</v>
@@ -32182,7 +32412,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>285</v>
+        <v>319</v>
       </c>
       <c r="C287">
         <v>677</v>
@@ -32289,7 +32519,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>286</v>
+        <v>320</v>
       </c>
       <c r="C288">
         <v>600</v>
@@ -32396,7 +32626,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>287</v>
+        <v>321</v>
       </c>
       <c r="C289">
         <v>1033</v>
@@ -32503,7 +32733,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="C290">
         <v>677</v>
@@ -32610,7 +32840,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>289</v>
+        <v>323</v>
       </c>
       <c r="C291">
         <v>710</v>
@@ -32717,7 +32947,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>290</v>
+        <v>324</v>
       </c>
       <c r="C292">
         <v>912</v>
@@ -32824,7 +33054,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>291</v>
+        <v>325</v>
       </c>
       <c r="C293">
         <v>870</v>
@@ -32931,7 +33161,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>292</v>
+        <v>326</v>
       </c>
       <c r="C294">
         <v>865</v>
@@ -33038,7 +33268,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>293</v>
+        <v>327</v>
       </c>
       <c r="C295">
         <v>752</v>
@@ -33145,7 +33375,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>294</v>
+        <v>328</v>
       </c>
       <c r="C296">
         <v>789</v>
@@ -33252,7 +33482,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>295</v>
+        <v>329</v>
       </c>
       <c r="C297">
         <v>875</v>
@@ -33359,7 +33589,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>296</v>
+        <v>330</v>
       </c>
       <c r="C298">
         <v>940</v>
@@ -33466,7 +33696,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>297</v>
+        <v>331</v>
       </c>
       <c r="C299">
         <v>628</v>
@@ -33573,7 +33803,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>298</v>
+        <v>332</v>
       </c>
       <c r="C300">
         <v>605</v>
@@ -33680,7 +33910,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>299</v>
+        <v>333</v>
       </c>
       <c r="C301">
         <v>662</v>
@@ -33787,7 +34017,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="C302">
         <v>956</v>
@@ -33894,7 +34124,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="C303">
         <v>914</v>
@@ -34001,7 +34231,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>302</v>
+        <v>336</v>
       </c>
       <c r="C304">
         <v>1205</v>
@@ -34108,7 +34338,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>303</v>
+        <v>337</v>
       </c>
       <c r="C305">
         <v>634</v>
@@ -34215,7 +34445,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>304</v>
+        <v>338</v>
       </c>
       <c r="C306">
         <v>1175</v>
@@ -34322,7 +34552,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>305</v>
+        <v>339</v>
       </c>
       <c r="C307">
         <v>647</v>
@@ -34429,7 +34659,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>306</v>
+        <v>340</v>
       </c>
       <c r="C308">
         <v>593</v>
@@ -34536,7 +34766,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>307</v>
+        <v>341</v>
       </c>
       <c r="C309">
         <v>927</v>
@@ -34643,7 +34873,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="C310">
         <v>774</v>
@@ -34750,7 +34980,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>309</v>
+        <v>343</v>
       </c>
       <c r="C311">
         <v>1004</v>
@@ -34857,7 +35087,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>310</v>
+        <v>344</v>
       </c>
       <c r="C312">
         <v>780</v>
@@ -34964,7 +35194,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>311</v>
+        <v>345</v>
       </c>
       <c r="C313">
         <v>1083</v>
@@ -35071,7 +35301,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="C314">
         <v>1231</v>
@@ -35178,7 +35408,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>313</v>
+        <v>347</v>
       </c>
       <c r="C315">
         <v>1059</v>
@@ -35285,7 +35515,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>314</v>
+        <v>348</v>
       </c>
       <c r="C316">
         <v>1023</v>
@@ -35392,7 +35622,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>315</v>
+        <v>349</v>
       </c>
       <c r="C317">
         <v>1171</v>
@@ -35499,7 +35729,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>316</v>
+        <v>350</v>
       </c>
       <c r="C318">
         <v>976</v>
@@ -35606,7 +35836,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>317</v>
+        <v>351</v>
       </c>
       <c r="C319">
         <v>1001</v>
@@ -35713,7 +35943,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>318</v>
+        <v>352</v>
       </c>
       <c r="C320">
         <v>1104</v>
@@ -35820,7 +36050,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>319</v>
+        <v>353</v>
       </c>
       <c r="C321">
         <v>1114</v>
@@ -35927,7 +36157,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
       <c r="C322">
         <v>1028</v>
@@ -36034,7 +36264,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>321</v>
+        <v>355</v>
       </c>
       <c r="C323">
         <v>969</v>
@@ -36141,7 +36371,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>322</v>
+        <v>356</v>
       </c>
       <c r="C324">
         <v>1098</v>
@@ -36248,7 +36478,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>323</v>
+        <v>357</v>
       </c>
       <c r="C325">
         <v>1044</v>
@@ -36355,7 +36585,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>324</v>
+        <v>358</v>
       </c>
       <c r="C326">
         <v>636</v>
@@ -36462,7 +36692,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>325</v>
+        <v>359</v>
       </c>
       <c r="C327">
         <v>615</v>
@@ -36569,7 +36799,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>326</v>
+        <v>360</v>
       </c>
       <c r="C328">
         <v>659</v>
@@ -36676,7 +36906,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>327</v>
+        <v>361</v>
       </c>
       <c r="C329">
         <v>1120</v>
@@ -36783,7 +37013,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>328</v>
+        <v>362</v>
       </c>
       <c r="C330">
         <v>1132</v>
@@ -36890,7 +37120,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>329</v>
+        <v>363</v>
       </c>
       <c r="C331">
         <v>1001</v>
@@ -36997,7 +37227,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="C332">
         <v>671</v>
@@ -37104,7 +37334,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="C333">
         <v>604</v>
@@ -37211,7 +37441,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>332</v>
+        <v>366</v>
       </c>
       <c r="C334">
         <v>510</v>
@@ -37318,7 +37548,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="C335">
         <v>696</v>
@@ -37425,7 +37655,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>334</v>
+        <v>368</v>
       </c>
       <c r="C336">
         <v>913</v>
@@ -37532,7 +37762,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>335</v>
+        <v>369</v>
       </c>
       <c r="C337">
         <v>764</v>
@@ -37639,7 +37869,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>336</v>
+        <v>370</v>
       </c>
       <c r="C338">
         <v>877</v>
@@ -37746,7 +37976,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>337</v>
+        <v>371</v>
       </c>
       <c r="C339">
         <v>992</v>
@@ -37853,7 +38083,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>338</v>
+        <v>372</v>
       </c>
       <c r="C340">
         <v>574</v>
@@ -37960,7 +38190,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>339</v>
+        <v>373</v>
       </c>
       <c r="C341">
         <v>732</v>
@@ -38067,7 +38297,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="C342">
         <v>1043</v>
@@ -38174,7 +38404,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="C343">
         <v>1009</v>
@@ -38281,7 +38511,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>342</v>
+        <v>376</v>
       </c>
       <c r="C344">
         <v>1238</v>
@@ -38388,7 +38618,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>343</v>
+        <v>377</v>
       </c>
       <c r="C345">
         <v>973</v>
@@ -38495,7 +38725,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>344</v>
+        <v>378</v>
       </c>
       <c r="C346">
         <v>985</v>
@@ -38602,7 +38832,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>345</v>
+        <v>379</v>
       </c>
       <c r="C347">
         <v>740</v>
@@ -38709,7 +38939,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>346</v>
+        <v>380</v>
       </c>
       <c r="C348">
         <v>741</v>
@@ -38816,7 +39046,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>347</v>
+        <v>381</v>
       </c>
       <c r="C349">
         <v>726</v>
@@ -38923,7 +39153,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>348</v>
+        <v>382</v>
       </c>
       <c r="C350">
         <v>682</v>
@@ -39030,7 +39260,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>349</v>
+        <v>383</v>
       </c>
       <c r="C351">
         <v>733</v>
@@ -39137,7 +39367,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="C352">
         <v>760</v>
@@ -39244,7 +39474,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>351</v>
+        <v>385</v>
       </c>
       <c r="C353">
         <v>927</v>
@@ -39351,7 +39581,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>352</v>
+        <v>386</v>
       </c>
       <c r="C354">
         <v>954</v>
@@ -39458,7 +39688,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>353</v>
+        <v>387</v>
       </c>
       <c r="C355">
         <v>899</v>
@@ -39565,7 +39795,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>354</v>
+        <v>388</v>
       </c>
       <c r="C356">
         <v>858</v>
@@ -39672,7 +39902,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="C357">
         <v>957</v>
@@ -39779,7 +40009,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>356</v>
+        <v>390</v>
       </c>
       <c r="C358">
         <v>916</v>
@@ -39886,7 +40116,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>357</v>
+        <v>391</v>
       </c>
       <c r="C359">
         <v>874</v>
@@ -39993,7 +40223,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>358</v>
+        <v>392</v>
       </c>
       <c r="C360">
         <v>930</v>
@@ -40100,7 +40330,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>359</v>
+        <v>393</v>
       </c>
       <c r="C361">
         <v>965</v>
@@ -40207,7 +40437,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>360</v>
+        <v>394</v>
       </c>
       <c r="C362">
         <v>937</v>
@@ -40314,7 +40544,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="C363">
         <v>874</v>
@@ -40421,7 +40651,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>362</v>
+        <v>396</v>
       </c>
       <c r="C364">
         <v>752</v>
@@ -40528,7 +40758,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>363</v>
+        <v>397</v>
       </c>
       <c r="C365">
         <v>711</v>
@@ -40635,7 +40865,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>364</v>
+        <v>398</v>
       </c>
       <c r="C366">
         <v>890</v>
@@ -40742,7 +40972,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="C367">
         <v>909</v>
@@ -40849,7 +41079,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="C368">
         <v>659</v>
@@ -40956,7 +41186,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>367</v>
+        <v>401</v>
       </c>
       <c r="C369">
         <v>671</v>
@@ -41063,7 +41293,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="C370">
         <v>1109</v>
@@ -41170,7 +41400,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>369</v>
+        <v>403</v>
       </c>
       <c r="C371">
         <v>976</v>
@@ -41277,7 +41507,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>370</v>
+        <v>404</v>
       </c>
       <c r="C372">
         <v>1015</v>
@@ -41384,7 +41614,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>371</v>
+        <v>405</v>
       </c>
       <c r="C373">
         <v>1036</v>
@@ -41491,7 +41721,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C374">
         <v>1057</v>
@@ -41598,7 +41828,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="C375">
         <v>980</v>
@@ -41705,7 +41935,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="C376">
         <v>1199</v>
@@ -41812,7 +42042,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="C377">
         <v>1192</v>
@@ -41919,7 +42149,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
       <c r="C378">
         <v>1057</v>
@@ -42026,7 +42256,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>377</v>
+        <v>411</v>
       </c>
       <c r="C379">
         <v>992</v>
@@ -42133,7 +42363,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="C380">
         <v>995</v>
@@ -42240,7 +42470,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="C381">
         <v>1039</v>
@@ -42347,7 +42577,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="C382">
         <v>868</v>
@@ -42454,7 +42684,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="C383">
         <v>977</v>
@@ -42561,7 +42791,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="C384">
         <v>912</v>
@@ -42668,7 +42898,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="C385">
         <v>936</v>
@@ -42775,7 +43005,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>384</v>
+        <v>418</v>
       </c>
       <c r="C386">
         <v>914</v>
@@ -42882,7 +43112,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>385</v>
+        <v>419</v>
       </c>
       <c r="C387">
         <v>590</v>
@@ -42989,7 +43219,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>386</v>
+        <v>420</v>
       </c>
       <c r="C388">
         <v>1159</v>
@@ -43096,7 +43326,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>387</v>
+        <v>421</v>
       </c>
       <c r="C389">
         <v>997</v>
@@ -43203,7 +43433,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>388</v>
+        <v>422</v>
       </c>
       <c r="C390">
         <v>948</v>
@@ -43310,7 +43540,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>389</v>
+        <v>423</v>
       </c>
       <c r="C391">
         <v>863</v>
@@ -43417,7 +43647,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>390</v>
+        <v>424</v>
       </c>
       <c r="C392">
         <v>699</v>
@@ -43524,7 +43754,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>391</v>
+        <v>425</v>
       </c>
       <c r="C393">
         <v>669</v>
@@ -43631,7 +43861,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="C394">
         <v>870</v>
@@ -43738,7 +43968,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>393</v>
+        <v>427</v>
       </c>
       <c r="C395">
         <v>818</v>
@@ -43845,7 +44075,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="C396">
         <v>989</v>
@@ -43952,7 +44182,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>395</v>
+        <v>429</v>
       </c>
       <c r="C397">
         <v>590</v>
@@ -44059,7 +44289,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>396</v>
+        <v>430</v>
       </c>
       <c r="C398">
         <v>1082</v>
@@ -44166,7 +44396,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>397</v>
+        <v>431</v>
       </c>
       <c r="C399">
         <v>1204</v>
@@ -44273,7 +44503,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>398</v>
+        <v>432</v>
       </c>
       <c r="C400">
         <v>1063</v>
@@ -44380,7 +44610,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>399</v>
+        <v>433</v>
       </c>
       <c r="C401">
         <v>1149</v>
@@ -44487,7 +44717,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>400</v>
+        <v>434</v>
       </c>
       <c r="C402">
         <v>904</v>
@@ -44594,7 +44824,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>401</v>
+        <v>435</v>
       </c>
       <c r="C403">
         <v>744</v>
@@ -44701,7 +44931,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="C404">
         <v>993</v>
@@ -44808,7 +45038,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="C405">
         <v>1072</v>
@@ -44915,7 +45145,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>404</v>
+        <v>438</v>
       </c>
       <c r="C406">
         <v>737</v>
@@ -45022,7 +45252,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>405</v>
+        <v>439</v>
       </c>
       <c r="C407">
         <v>747</v>
@@ -45129,7 +45359,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>406</v>
+        <v>440</v>
       </c>
       <c r="C408">
         <v>1049</v>
@@ -45236,7 +45466,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>407</v>
+        <v>441</v>
       </c>
       <c r="C409">
         <v>989</v>
@@ -45343,7 +45573,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>408</v>
+        <v>442</v>
       </c>
       <c r="C410">
         <v>928</v>
@@ -45450,7 +45680,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="C411">
         <v>1110</v>
@@ -45557,7 +45787,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>410</v>
+        <v>444</v>
       </c>
       <c r="C412">
         <v>986</v>
